--- a/qa/manual/Buku-Kasus-Uji-QA.xlsx
+++ b/qa/manual/Buku-Kasus-Uji-QA.xlsx
@@ -2487,7 +2487,7 @@
 2. Tekan lagi untuk berhenti.</t>
   </si>
   <si>
-    <t xml:space="preserve">Muncul "Mengenali suaramu..." lalu kolom ketik terisi teks hasil pengenalan dengan keterangan "Begini yang terdengar. Perbaiki kalau ada yang salah, lalu kirim." (atau pesan "tidak terdengar jelas" bila suara tidak dikenali).</t>
+    <t xml:space="preserve">Muncul "Mengenali suaramu..." lalu kolom ketik terisi teks hasil pengenalan dengan keterangan "Begini yang terdengar. Perbaiki kalau ada yang salah, lalu kirim." (atau pesan "tidak terdengar jelas" bila suara tidak dikenali). Bila pengenalan suara belum diaktifkan di server: muncul SATU keterangan "Fitur suara belum diaktifkan di server ini. Kamu tetap bisa mengetik jawabanmu." (tidak ganda), tombol mikrofon mati, dan mengetik tetap berfungsi.</t>
   </si>
   <si>
     <t xml:space="preserve">AI-04, AI-05</t>
@@ -2558,7 +2558,7 @@
     <t xml:space="preserve">1. Buka layar chat, ketik kalimat dan kirim.</t>
   </si>
   <si>
-    <t xml:space="preserve">Muncul peringatan "Fitur ngobrol dengan AI belum diaktifkan di server ini. Hubungi admin lembaga."; kalimat murid kembali ke kolom ketik; jatah tidak berkurang; tidak ada layar kosong.</t>
+    <t xml:space="preserve">Muncul peringatan "Fitur ngobrol dengan AI belum diaktifkan di server ini. Hubungi admin lembaga."; kalimat murid kembali ke kolom ketik; jatah tidak berkurang; tidak ada layar kosong. Hanya satu pesan yang tampil: keterangan suara yang menyuruh "tetap bisa mengetik" (bila sempat muncul) hilang karena kolom ketik kini mati.</t>
   </si>
   <si>
     <t xml:space="preserve">AI-14</t>
@@ -14218,7 +14218,7 @@
       <c r="Q102" s="27"/>
       <c r="R102" s="16"/>
     </row>
-    <row r="103" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="117" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="21" t="n">
         <v>99</v>
       </c>
@@ -14308,7 +14308,7 @@
       <c r="Q104" s="27"/>
       <c r="R104" s="16"/>
     </row>
-    <row r="105" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="21" t="n">
         <v>101</v>
       </c>
